--- a/descriptive tables/remittance_households.xlsx
+++ b/descriptive tables/remittance_households.xlsx
@@ -12,12 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t xml:space="preserve">province</t>
   </si>
   <si>
     <t xml:space="preserve">hhlds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent</t>
   </si>
 </sst>
 </file>
@@ -353,13 +356,19 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>248</v>
+        <v>288</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6.72897196261682</v>
       </c>
     </row>
     <row r="3">
@@ -367,7 +376,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>219</v>
+        <v>323</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.54672897196262</v>
       </c>
     </row>
     <row r="4">
@@ -375,7 +387,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>380</v>
+        <v>551</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12.8738317757009</v>
       </c>
     </row>
     <row r="5">
@@ -383,7 +398,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>270</v>
+        <v>291</v>
+      </c>
+      <c r="C5" t="n">
+        <v>6.79906542056075</v>
       </c>
     </row>
     <row r="6">
@@ -391,7 +409,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>222</v>
+        <v>314</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7.33644859813084</v>
       </c>
     </row>
     <row r="7">
@@ -399,7 +420,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>228</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.32710280373832</v>
       </c>
     </row>
     <row r="8">
@@ -407,7 +431,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>244</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.70093457943925</v>
       </c>
     </row>
   </sheetData>
